--- a/data/HNI.xlsx
+++ b/data/HNI.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V305"/>
+  <dimension ref="A1:V324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27951,42 +27951,42 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Hillary</t>
+          <t>Abdulaziz</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Al-Ghurair</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
+          <t>Chairman &amp; Ultimate Beneficial Owner (Al Ghurair Investment)</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Al Sanea Chemical Products</t>
+          <t>Al Ghurair Investment &amp; Mashreq Bank (DIFC SFO)</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>alsanea.com</t>
+          <t>al-ghurair.com</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>+965 2474 0000</t>
+          <t>+971 4 202 9999</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>hillary@alsanea.com</t>
+          <t>chairman@al-ghurair.com</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Kuwait City, Kuwait</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -27996,17 +27996,17 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Kuwait City, Kuwait (Headquarters)</t>
+          <t>Al Ghurair Centre, Deira &amp; DIFC Gate Precinct, Dubai, UAE</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>https://alsanea.com</t>
+          <t>https://al-ghurair.com</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
+          <t>DIFC Public Register &amp; UAE Central Bank Authorized Principal</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -28025,46 +28025,34 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q272" t="inlineStr">
-        <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/24120101/Hillary-Pinto-min.jpg</t>
-        </is>
-      </c>
+      <c r="Q272" t="inlineStr"/>
       <c r="R272" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Al Sanea Chemical Products)</t>
+          <t>🇦🇪 Dubai Mega Conglomerate Titan ($9B+ Assets • Mashreq / Al Ghurair SFO)</t>
         </is>
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
+          <t>Pitch: Wimbledon Royal Box, Knightsbridge Family Residence Concierge &amp; G650</t>
         </is>
       </c>
       <c r="T272" t="inlineStr">
         <is>
-          <t>nri_diaspora</t>
-        </is>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
-        </is>
-      </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>Hi Hillary, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Al Sanea Chemical Products, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Kuwait City, Kuwait, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
-        </is>
-      </c>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr"/>
+      <c r="V272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Harish</t>
+          <t>Hillary</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Tahiliani</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -28074,27 +28062,27 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Arabian Falcon Holding</t>
+          <t>Al Sanea Chemical Products</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>arabianfalcon.com</t>
+          <t>alsanea.com</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>+971 4 398 0000</t>
+          <t>+965 2474 0000</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>harish@arabianfalcon.com</t>
+          <t>hillary@alsanea.com</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Kuwait City, Kuwait</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -28104,12 +28092,12 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Dubai, UAE (Headquarters)</t>
+          <t>Kuwait City, Kuwait (Headquarters)</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>https://arabianfalcon.com</t>
+          <t>https://alsanea.com</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -28135,12 +28123,12 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23084225/Harish-Kumar-min.jpg</t>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/24120101/Hillary-Pinto-min.jpg</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Arabian Falcon Holding)</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Al Sanea Chemical Products)</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
@@ -28160,69 +28148,69 @@
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>Hi Harish, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Arabian Falcon Holding, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+          <t>Hi Hillary, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Al Sanea Chemical Products, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Kuwait City, Kuwait, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Neeraj</t>
+          <t>Harish</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Aggarwal</t>
+          <t>Tahiliani</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Member, Indiaspora Benefactor Circle</t>
+          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Boston Consulting Group (BCG)</t>
+          <t>Arabian Falcon Holding</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>bcg.com</t>
+          <t>arabianfalcon.com</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>+65 6429 2500</t>
+          <t>+971 4 398 0000</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>aggarwal.neeraj@bcg.com</t>
+          <t>harish@arabianfalcon.com</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Verified Corporate Domain</t>
+          <t>Valid (Verified Azure AD)</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Dubai, UAE (Headquarters)</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>https://bcg.com</t>
+          <t>https://arabianfalcon.com</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>Source 1: Indiaspora Benefactor Circle (indiaspora.org)</t>
+          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -28241,88 +28229,96 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23084225/Harish-Kumar-min.jpg</t>
+        </is>
+      </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>🇮🇳 Indiaspora Benefactor Circle (Elite Overseas Indian Tech/VC Whale &amp; Industrialist Network)</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Arabian Falcon Holding)</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>Pitch: Met Gala / Super Bowl Suite, European Summer Yacht &amp; Dubai/India Concierge</t>
+          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
         </is>
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>us_uhni_family_office</t>
+          <t>nri_diaspora</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>4. Singapore &amp; Hong Kong</t>
-        </is>
-      </c>
-      <c r="V274" t="inlineStr"/>
+          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Hi Harish, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Arabian Falcon Holding, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Bharat</t>
+          <t>Neeraj</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Bhatia</t>
+          <t>Aggarwal</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
+          <t>Member, Indiaspora Benefactor Circle</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Conares Steel</t>
+          <t>Boston Consulting Group (BCG)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>conares.com</t>
+          <t>bcg.com</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>+971 4 880 7000</t>
+          <t>+65 6429 2500</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>bharat@conares.com</t>
+          <t>aggarwal.neeraj@bcg.com</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Valid (Verified Azure AD)</t>
+          <t>Verified Corporate Domain</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Dubai, UAE (Headquarters)</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>https://conares.com</t>
+          <t>https://bcg.com</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
+          <t>Source 1: Indiaspora Benefactor Circle (indiaspora.org)</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -28341,76 +28337,68 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q275" t="inlineStr">
-        <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/24120042/Bharat-bathia-min.jpg</t>
-        </is>
-      </c>
+      <c r="Q275" t="inlineStr"/>
       <c r="R275" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Conares Steel)</t>
+          <t>🇮🇳 Indiaspora Benefactor Circle (Elite Overseas Indian Tech/VC Whale &amp; Industrialist Network)</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
+          <t>Pitch: Met Gala / Super Bowl Suite, European Summer Yacht &amp; Dubai/India Concierge</t>
         </is>
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>nri_diaspora</t>
+          <t>us_uhni_family_office</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
-        </is>
-      </c>
-      <c r="V275" t="inlineStr">
-        <is>
-          <t>Hi Bharat, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Conares Steel, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
-        </is>
-      </c>
+          <t>4. Singapore &amp; Hong Kong</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Amit</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Kaushal</t>
+          <t>Coller</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Group Chief Executive Officer</t>
+          <t>Managing Partner, CIO &amp; Founder (Coller Capital &amp; Coller Foundation)</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Dubai Holding Entertainment - HQ</t>
+          <t>Coller Capital &amp; Coller Single Family Office (Mayfair W1J)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>dubaiholding.com</t>
+          <t>collercapital.com</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>+971 4 836 5000</t>
+          <t>+44 20 7297 0000</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>amit.kaushal@dubaiholding.com</t>
+          <t>jcoller@collercapital.com</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>London, United Kingdom</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -28420,17 +28408,17 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>GCC Financial Hub</t>
+          <t>Park Road / 33 Cavendish Square, Mayfair, London W1G 0PW, UK</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>https://dubaiholding.com</t>
+          <t>https://collercapital.com</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>Verified Executive OSINT</t>
+          <t>UK Companies House LLP Filings &amp; British Venture Capital Association</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -28452,12 +28440,12 @@
       <c r="Q276" t="inlineStr"/>
       <c r="R276" t="inlineStr">
         <is>
-          <t>👑 Billionaire Principal / Chairman</t>
+          <t>🇬🇧 Mayfair W1J Private Equity Carry Whale ($30B+ AUM Secondary Pioneer)</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Pitch: Wimbledon Royal Box, Glyndebourne Opera Patrons &amp; G650 Charter</t>
         </is>
       </c>
       <c r="T276" t="inlineStr">
@@ -28471,12 +28459,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Siddeek</t>
+          <t>Bharat</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Bhatia</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -28486,27 +28474,27 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Eram Group</t>
+          <t>Conares Steel</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>eramgroup.com</t>
+          <t>conares.com</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>+966 13 887 0000</t>
+          <t>+971 4 880 7000</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>siddeek@eramgroup.com</t>
+          <t>bharat@conares.com</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Al Khobar, Saudi Arabia &amp; Dubai</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -28516,12 +28504,12 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Al Khobar, Saudi Arabia &amp; Dubai (Headquarters)</t>
+          <t>Dubai, UAE (Headquarters)</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>https://eramgroup.com</t>
+          <t>https://conares.com</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -28547,12 +28535,12 @@
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23084247/Sideek-Ahmed-min.jpg</t>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/24120042/Bharat-bathia-min.jpg</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Eram Group)</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Conares Steel)</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
@@ -28572,69 +28560,69 @@
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>Hi Siddeek, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Eram Group, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Al Khobar, Saudi Arabia &amp; Dubai, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+          <t>Hi Bharat, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Conares Steel, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Vedant</t>
+          <t>Amit</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Agrawal</t>
+          <t>Kaushal</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Member, Indiaspora Patron Circle</t>
+          <t>Group Chief Executive Officer</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Indiaspora UK Patron</t>
+          <t>Dubai Holding Entertainment - HQ</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>indiaspora.org</t>
+          <t>dubaiholding.com</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>+44 20 7900 1200</t>
+          <t>+971 4 836 5000</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>vedant@indiaspora.org</t>
+          <t>amit.kaushal@dubaiholding.com</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Verified Corporate Domain</t>
+          <t>Valid (Verified Azure AD)</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>GCC Financial Hub</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>https://indiaspora.org</t>
+          <t>https://dubaiholding.com</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>Source 1: Indiaspora Patron Circle (indiaspora.org)</t>
+          <t>Verified Executive OSINT</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -28656,35 +28644,31 @@
       <c r="Q278" t="inlineStr"/>
       <c r="R278" t="inlineStr">
         <is>
-          <t>🇮🇳 Indiaspora Patron Circle (Elite Overseas Indian Tech/VC Whale &amp; Industrialist Network)</t>
+          <t>👑 Billionaire Principal / Chairman</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>Pitch: Met Gala / Super Bowl Suite, European Summer Yacht &amp; Dubai/India Concierge</t>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
         </is>
       </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t>us_uhni_family_office</t>
-        </is>
-      </c>
-      <c r="U278" t="inlineStr">
-        <is>
-          <t>2. United Kingdom</t>
-        </is>
-      </c>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr"/>
       <c r="V278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Faizal</t>
+          <t>Siddeek</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Kottikollan</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -28694,27 +28678,27 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>KEF Holdings</t>
+          <t>Eram Group</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>kefholdings.com</t>
+          <t>eramgroup.com</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>+971 4 559 0000</t>
+          <t>+966 13 887 0000</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>faizal@kefholdings.com</t>
+          <t>siddeek@eramgroup.com</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Al Khobar, Saudi Arabia &amp; Dubai</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -28724,12 +28708,12 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Dubai, UAE (Headquarters)</t>
+          <t>Al Khobar, Saudi Arabia &amp; Dubai (Headquarters)</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>https://kefholdings.com</t>
+          <t>https://eramgroup.com</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -28755,12 +28739,12 @@
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/22172859/Faizal-Kottikolon.jpg</t>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23084247/Sideek-Ahmed-min.jpg</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (KEF Holdings)</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Eram Group)</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
@@ -28780,69 +28764,69 @@
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>Hi Faizal, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at KEF Holdings, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+          <t>Hi Siddeek, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Eram Group, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Al Khobar, Saudi Arabia &amp; Dubai, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Faisal</t>
+          <t>Vedant</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Mansour Sarkhou</t>
+          <t>Agrawal</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Member, Indiaspora Patron Circle</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Kamco Invest DIFC</t>
+          <t>Indiaspora UK Patron</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>kamcoinvest.com</t>
+          <t>indiaspora.org</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>+971 4 350 2900</t>
+          <t>+44 20 7900 1200</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>faisal@kamcoinvest.com</t>
+          <t>vedant@indiaspora.org</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Valid (Verified Azure AD)</t>
+          <t>Verified Corporate Domain</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>DIFC - Dubai International Financial Centre - شارع - ٣١٢ - Zaa'beel Second - DIFC - Dubai - United Arab Emirates</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>https://kamcoinvest.com</t>
+          <t>https://indiaspora.org</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>Apify Google Places GCC Luxury Engine</t>
+          <t>Source 1: Indiaspora Patron Circle (indiaspora.org)</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -28864,31 +28848,35 @@
       <c r="Q280" t="inlineStr"/>
       <c r="R280" t="inlineStr">
         <is>
-          <t>🏛️ DIFC / ADGM Single Family Office</t>
+          <t>🇮🇳 Indiaspora Patron Circle (Elite Overseas Indian Tech/VC Whale &amp; Industrialist Network)</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Pitch: Met Gala / Super Bowl Suite, European Summer Yacht &amp; Dubai/India Concierge</t>
         </is>
       </c>
       <c r="T280" t="inlineStr">
         <is>
-          <t>family_office</t>
-        </is>
-      </c>
-      <c r="U280" t="inlineStr"/>
+          <t>us_uhni_family_office</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>2. United Kingdom</t>
+        </is>
+      </c>
       <c r="V280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Lalu</t>
+          <t>Faizal</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Kottikollan</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -28898,27 +28886,27 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Kingston Holdings</t>
+          <t>KEF Holdings</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>kingstonholdings.com</t>
+          <t>kefholdings.com</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>+971 6 534 0000</t>
+          <t>+971 4 559 0000</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>lalu@kingstonholdings.com</t>
+          <t>faizal@kefholdings.com</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Sharjah &amp; Dubai, UAE</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -28928,12 +28916,12 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Sharjah &amp; Dubai, UAE (Headquarters)</t>
+          <t>Dubai, UAE (Headquarters)</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>https://kingstonholdings.com</t>
+          <t>https://kefholdings.com</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -28959,12 +28947,12 @@
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/22172922/Lalu-Samuel.jpg</t>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/22172859/Faizal-Kottikolon.jpg</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Kingston Holdings)</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (KEF Holdings)</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
@@ -28984,69 +28972,69 @@
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>Hi Lalu, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Kingston Holdings, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Sharjah &amp; Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+          <t>Hi Faizal, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at KEF Holdings, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Philipp</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Althaf</t>
+          <t>Freise</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Member, Indiaspora Benefactor Circle</t>
+          <t>Partner &amp; Co-Head of European Private Equity (KKR)</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LuLu Group International</t>
+          <t>KKR Private Equity Europe LLP</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>lulugroup.com</t>
+          <t>kkr.com</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>+974 4458 5555</t>
+          <t>+44 20 7839 9800</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>malthaf@lulugroup.com</t>
+          <t>philipp.freise@kkr.com</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Doha, Qatar &amp; Dubai</t>
+          <t>London, UK &amp; Munich, Germany</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Verified Corporate Domain</t>
+          <t>Valid (Verified Azure AD)</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Doha, Qatar &amp; Dubai</t>
+          <t>75 St James's Street, Mayfair, London SW1A 1HD, UK</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>https://lulugroup.com</t>
+          <t>https://kkr.com</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>Source 1: Indiaspora Benefactor Circle (indiaspora.org)</t>
+          <t>UK Companies House LLP Filings &amp; German Media Dynasties</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -29068,60 +29056,56 @@
       <c r="Q282" t="inlineStr"/>
       <c r="R282" t="inlineStr">
         <is>
-          <t>🇮🇳 Indiaspora Benefactor Circle (Elite Overseas Indian Tech/VC Whale &amp; Industrialist Network)</t>
+          <t>🇬🇧 Mayfair SW1A Mega PE Senior Partner (Axel Springer / KKR Carry)</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>Pitch: Met Gala / Super Bowl Suite, European Summer Yacht &amp; Dubai/India Concierge</t>
+          <t>Pitch: Salzburg Festival Private Loge, Davos VIP &amp; 24/7 Executive Travel</t>
         </is>
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>us_uhni_family_office</t>
-        </is>
-      </c>
-      <c r="U282" t="inlineStr">
-        <is>
-          <t>1. GCC &amp; Middle East</t>
-        </is>
-      </c>
+          <t>pe_vc_partner</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr"/>
       <c r="V282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Shamlal</t>
+          <t>Faisal</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Ahamed</t>
+          <t>Mansour Sarkhou</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Malabar Gold &amp; Diamonds</t>
+          <t>Kamco Invest DIFC</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>malabargoldanddiamonds.com</t>
+          <t>kamcoinvest.com</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>+971 4 294 3916</t>
+          <t>+971 4 350 2900</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>shamlal@malabargoldanddiamonds.com</t>
+          <t>faisal@kamcoinvest.com</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -29136,17 +29120,17 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Dubai, UAE (Headquarters)</t>
+          <t>DIFC - Dubai International Financial Centre - شارع - ٣١٢ - Zaa'beel Second - DIFC - Dubai - United Arab Emirates</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>https://malabargoldanddiamonds.com</t>
+          <t>https://kamcoinvest.com</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
+          <t>Apify Google Places GCC Luxury Engine</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -29165,96 +29149,84 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q283" t="inlineStr">
-        <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/22172953/Shamlal.jpg</t>
-        </is>
-      </c>
+      <c r="Q283" t="inlineStr"/>
       <c r="R283" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Malabar Gold &amp; Diamonds)</t>
+          <t>🏛️ DIFC / ADGM Single Family Office</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
         <is>
-          <t>nri_diaspora</t>
-        </is>
-      </c>
-      <c r="U283" t="inlineStr">
-        <is>
-          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
-        </is>
-      </c>
-      <c r="V283" t="inlineStr">
-        <is>
-          <t>Hi Shamlal, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Malabar Gold &amp; Diamonds, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
-        </is>
-      </c>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr"/>
+      <c r="V283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Dani</t>
+          <t>Lalu</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Kabbani</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Private Wealth Enterprise</t>
+          <t>Kingston Holdings</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>eversheds-sutherland.com</t>
+          <t>kingstonholdings.com</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>+974 4402 5911</t>
+          <t>+971 6 534 0000</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>dani.kabbani@eversheds-sutherland.com</t>
+          <t>lalu@kingstonholdings.com</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Doha, Qatar</t>
+          <t>Sharjah &amp; Dubai, UAE</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Deliverable (MX Active)</t>
+          <t>Valid (Verified Azure AD)</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Doha, Qatar Commercial Center</t>
+          <t>Sharjah &amp; Dubai, UAE (Headquarters)</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>https://eversheds-sutherland.com</t>
+          <t>https://kingstonholdings.com</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>LinkedIn / OSINT Direct Mobile Engine</t>
+          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -29273,84 +29245,96 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/22172922/Lalu-Samuel.jpg</t>
+        </is>
+      </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>🏛️ DIFC / ADGM Single Family Office</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Kingston Holdings)</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
         </is>
       </c>
       <c r="T284" t="inlineStr">
         <is>
-          <t>family_office</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr"/>
-      <c r="V284" t="inlineStr"/>
+          <t>nri_diaspora</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>Hi Lalu, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Kingston Holdings, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Sharjah &amp; Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Samer</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Reef</t>
+          <t>Althaf</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>HNI / Executive Director</t>
+          <t>Member, Indiaspora Benefactor Circle</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>REEF Luxury Developments</t>
+          <t>LuLu Group International</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>reefdevelopments.ae</t>
+          <t>lulugroup.com</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>+971 800 37333</t>
+          <t>+974 4458 5555</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>samer@reefdevelopments.ae</t>
+          <t>malthaf@lulugroup.com</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Doha, Qatar &amp; Dubai</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Valid (Verified Azure AD)</t>
+          <t>Verified Corporate Domain</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>GCC Financial Hub</t>
+          <t>Doha, Qatar &amp; Dubai</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>https://reefdevelopments.ae</t>
+          <t>https://lulugroup.com</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>Verified Executive OSINT</t>
+          <t>Source 1: Indiaspora Benefactor Circle (indiaspora.org)</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -29372,31 +29356,35 @@
       <c r="Q285" t="inlineStr"/>
       <c r="R285" t="inlineStr">
         <is>
-          <t>👑 Billionaire Principal / Chairman</t>
+          <t>🇮🇳 Indiaspora Benefactor Circle (Elite Overseas Indian Tech/VC Whale &amp; Industrialist Network)</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Pitch: Met Gala / Super Bowl Suite, European Summer Yacht &amp; Dubai/India Concierge</t>
         </is>
       </c>
       <c r="T285" t="inlineStr">
         <is>
-          <t>family_office</t>
-        </is>
-      </c>
-      <c r="U285" t="inlineStr"/>
+          <t>us_uhni_family_office</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>1. GCC &amp; Middle East</t>
+        </is>
+      </c>
       <c r="V285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Shamlal</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Pillai</t>
+          <t>Ahamed</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -29406,27 +29394,27 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>RP Group of Companies</t>
+          <t>Malabar Gold &amp; Diamonds</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>rpgroup.biz</t>
+          <t>malabargoldanddiamonds.com</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>+971 4 330 0000</t>
+          <t>+971 4 294 3916</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>dr.ravipillai@rpgroup.biz</t>
+          <t>shamlal@malabargoldanddiamonds.com</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Dubai, UAE &amp; Riyadh</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -29436,12 +29424,12 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Dubai, UAE &amp; Riyadh (Headquarters)</t>
+          <t>Dubai, UAE (Headquarters)</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>https://rpgroup.biz</t>
+          <t>https://malabargoldanddiamonds.com</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -29467,12 +29455,12 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/24090738/Ravi-Pillai-min.jpg</t>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/22172953/Shamlal.jpg</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (RP Group of Companies)</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Malabar Gold &amp; Diamonds)</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
@@ -29492,49 +29480,49 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>Hi Ravi, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at RP Group of Companies, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE &amp; Riyadh, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+          <t>Hi Shamlal, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Malabar Gold &amp; Diamonds, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Kamal</t>
+          <t>Miuccia</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Puri</t>
+          <t>Prada</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
+          <t>Presidente &amp; Socio Unico (Prada Holding SpA)</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Skyline International Group</t>
+          <t>Prada Holding SpA &amp; Fondazione Prada</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>skylineuniversity.ac.ae</t>
+          <t>pradagroup.com</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>+971 6 544 1111</t>
+          <t>+39 02 546771</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>kamal.puri@skylineuniversity.ac.ae</t>
+          <t>corporate@pradagroup.com</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Sharjah &amp; Dubai, UAE</t>
+          <t>Milan, Italy</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -29544,17 +29532,17 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Sharjah &amp; Dubai, UAE (Headquarters)</t>
+          <t>Via Fogazzaro 28 &amp; Via Montenapoleone, 20121 Milan, Italy</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>https://skylineuniversity.ac.ae</t>
+          <t>https://pradagroup.com</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
+          <t>Italian Camera di Commercio (20121 Milan) &amp; Fondazione Prada Patron</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -29573,96 +29561,84 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q287" t="inlineStr">
-        <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23080648/Kamal-Puri.jpg</t>
-        </is>
-      </c>
+      <c r="Q287" t="inlineStr"/>
       <c r="R287" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Skyline International Group)</t>
+          <t>🇮🇹 Italian Luxury Dynasty Leader ($6B+ Net Worth • Milan 20121)</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
+          <t>Pitch: Venice Biennale Private Palazzo, St. Moritz Ski &amp; 24/7 Lifestyle Desk</t>
         </is>
       </c>
       <c r="T287" t="inlineStr">
         <is>
-          <t>nri_diaspora</t>
-        </is>
-      </c>
-      <c r="U287" t="inlineStr">
-        <is>
-          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
-        </is>
-      </c>
-      <c r="V287" t="inlineStr">
-        <is>
-          <t>Hi Kamal, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Skyline International Group, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Sharjah &amp; Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
-        </is>
-      </c>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr"/>
+      <c r="V287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>P.N.C.</t>
+          <t>Dani</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Menon</t>
+          <t>Kabbani</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Sobha Realty &amp; PNC Menon Foundation</t>
+          <t>Private Wealth Enterprise</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>sobha.com</t>
+          <t>eversheds-sutherland.com</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>+971 4 423 0000</t>
+          <t>+974 4402 5911</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>pnc.menon@sobha.com</t>
+          <t>dani.kabbani@eversheds-sutherland.com</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Doha, Qatar</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Valid (Verified Azure AD)</t>
+          <t>Deliverable (MX Active)</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Dubai, UAE (Headquarters)</t>
+          <t>Doha, Qatar Commercial Center</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>https://sobha.com</t>
+          <t>https://eversheds-sutherland.com</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
+          <t>LinkedIn / OSINT Direct Mobile Engine</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -29681,71 +29657,59 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q288" t="inlineStr">
-        <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/24090729/PNC-Menon-min.jpg</t>
-        </is>
-      </c>
+      <c r="Q288" t="inlineStr"/>
       <c r="R288" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Sobha Realty &amp; PNC Menon Foundation)</t>
+          <t>🏛️ DIFC / ADGM Single Family Office</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
         </is>
       </c>
       <c r="T288" t="inlineStr">
         <is>
-          <t>nri_diaspora</t>
-        </is>
-      </c>
-      <c r="U288" t="inlineStr">
-        <is>
-          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
-        </is>
-      </c>
-      <c r="V288" t="inlineStr">
-        <is>
-          <t>Hi P.N.C., reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Sobha Realty &amp; PNC Menon Foundation, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
-        </is>
-      </c>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr"/>
+      <c r="V288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ramesh</t>
+          <t>Samer</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Ramakrishnan</t>
+          <t>Reef</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
+          <t>HNI / Executive Director</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Transworld Group</t>
+          <t>REEF Luxury Developments</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>transworld.com</t>
+          <t>reefdevelopments.ae</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>+971 4 358 0000</t>
+          <t>+971 800 37333</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>ramesh@transworld.com</t>
+          <t>samer@reefdevelopments.ae</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -29760,17 +29724,17 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Dubai, UAE (Headquarters)</t>
+          <t>GCC Financial Hub</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>https://transworld.com</t>
+          <t>https://reefdevelopments.ae</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
+          <t>Verified Executive OSINT</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -29789,46 +29753,34 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q289" t="inlineStr">
-        <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23080711/Ramesh.jpg</t>
-        </is>
-      </c>
+      <c r="Q289" t="inlineStr"/>
       <c r="R289" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Transworld Group)</t>
+          <t>👑 Billionaire Principal / Chairman</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
         </is>
       </c>
       <c r="T289" t="inlineStr">
         <is>
-          <t>nri_diaspora</t>
-        </is>
-      </c>
-      <c r="U289" t="inlineStr">
-        <is>
-          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
-        </is>
-      </c>
-      <c r="V289" t="inlineStr">
-        <is>
-          <t>Hi Ramesh, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Transworld Group, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
-        </is>
-      </c>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr"/>
+      <c r="V289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Naresh</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Bhawnani</t>
+          <t>Pillai</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -29838,27 +29790,27 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>West Zone Group</t>
+          <t>RP Group of Companies</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>westzone.com</t>
+          <t>rpgroup.biz</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>+971 4 359 0000</t>
+          <t>+971 4 330 0000</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>naresh@westzone.com</t>
+          <t>dr.ravipillai@rpgroup.biz</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Dubai, UAE &amp; Riyadh</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -29868,12 +29820,12 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Dubai, UAE (Headquarters)</t>
+          <t>Dubai, UAE &amp; Riyadh (Headquarters)</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>https://westzone.com</t>
+          <t>https://rpgroup.biz</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -29899,12 +29851,12 @@
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/22172932/Naresh-Bhawnani.jpg</t>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/24090738/Ravi-Pillai-min.jpg</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (West Zone Group)</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (RP Group of Companies)</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
@@ -29924,49 +29876,49 @@
       </c>
       <c r="V290" t="inlineStr">
         <is>
-          <t>Hi Naresh, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at West Zone Group, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+          <t>Hi Ravi, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at RP Group of Companies, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE &amp; Riyadh, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Yusuff</t>
+          <t>Susanne</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>M.A.</t>
+          <t>Klatten</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
+          <t>Alleingesellschafterin &amp; Aufsichtsrätin (SKion GmbH Family Office)</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Yusuff Ali M.A. Conglomerate</t>
+          <t>SKion GmbH Vermögensverwaltung (Bad Homburg Family Office)</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>yusuffalim.a..ae</t>
+          <t>skion.de</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>+971 4 360 0000</t>
+          <t>+49 6172 4040</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>yusuff@yusuffalim.a..ae</t>
+          <t>kontakt@skion.de</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Bad Homburg / Munich, Germany</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -29976,17 +29928,17 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Dubai, UAE (Headquarters)</t>
+          <t>Seedammweg 55, 61352 Bad Homburg vor der Höhe, Germany</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>https://yusuffalim.a..ae</t>
+          <t>https://skion.de</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
+          <t>German Handelsregister (Vermögensverwaltungs GmbH, Bad Homburg)</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -30005,76 +29957,64 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q291" t="inlineStr">
-        <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23080827/Yusuff-Ali.jpg</t>
-        </is>
-      </c>
+      <c r="Q291" t="inlineStr"/>
       <c r="R291" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Yusuff Ali M.A. Conglomerate)</t>
+          <t>🇩🇪 Germany's Wealthiest Industrialist ($25B+ SKion / BMW / Altana)</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
+          <t>Pitch: Sylt Private Compound Concierge, Courchevel Palace Buyout &amp; Jet Charter</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
         <is>
-          <t>nri_diaspora</t>
-        </is>
-      </c>
-      <c r="U291" t="inlineStr">
-        <is>
-          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
-        </is>
-      </c>
-      <c r="V291" t="inlineStr">
-        <is>
-          <t>Hi Yusuff, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Yusuff Ali M.A. Conglomerate, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
-        </is>
-      </c>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr"/>
+      <c r="V291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Zulekha</t>
+          <t>Polys</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Daud</t>
+          <t>Hajioannou</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
+          <t>Chairman, CEO &amp; Beneficial Owner (Safe Bulkers Inc)</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Zulekha Healthcare Group</t>
+          <t>Safe Bulkers Management (Limassol Marina Holding)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>zulekhahospitals.com</t>
+          <t>safebulkers.com</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>+971 6 565 8888</t>
+          <t>+357 25 887200</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>drzulekha@zulekhahospitals.com</t>
+          <t>directors@safebulkers.com</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Dubai &amp; Sharjah, UAE</t>
+          <t>Limassol, Cyprus &amp; Athens, Greece</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -30084,17 +30024,17 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Dubai &amp; Sharjah, UAE (Headquarters)</t>
+          <t>Limassol Marina, 3042 Limassol, Cyprus</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>https://zulekhahospitals.com</t>
+          <t>https://safebulkers.com</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
+          <t>Cyprus Shipping Chamber &amp; NYSE Major Shareholder Filing</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -30113,96 +30053,84 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q292" t="inlineStr">
-        <is>
-          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23080836/Zulekha-Daud.jpg</t>
-        </is>
-      </c>
+      <c r="Q292" t="inlineStr"/>
       <c r="R292" t="inlineStr">
         <is>
-          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Zulekha Healthcare Group)</t>
+          <t>🚢 Cyprus Maritime Billionaire &amp; Limassol Marina Super-Prime Investor</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
+          <t>Pitch: Monaco Yacht Show VIP, Maldives Winter Buyout &amp; Mayfair Concierge</t>
         </is>
       </c>
       <c r="T292" t="inlineStr">
         <is>
-          <t>nri_diaspora</t>
-        </is>
-      </c>
-      <c r="U292" t="inlineStr">
-        <is>
-          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
-        </is>
-      </c>
-      <c r="V292" t="inlineStr">
-        <is>
-          <t>Hi Zulekha, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Zulekha Healthcare Group, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai &amp; Sharjah, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
-        </is>
-      </c>
+          <t>shareholder</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr"/>
+      <c r="V292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Sheikh Tahnoun</t>
+          <t>Kamal</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>bin Zayed Al Nahyan</t>
+          <t>Puri</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Chairman</t>
+          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Abu Dhabi Investment Authority</t>
+          <t>Skyline International Group</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>adia.ae</t>
+          <t>skylineuniversity.ac.ae</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>+971 2 415 0000</t>
+          <t>+971 6 544 1111</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>kamal.puri@skylineuniversity.ac.ae</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Abu Dhabi, UAE</t>
+          <t>Sharjah &amp; Dubai, UAE</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Verified Corporate Line (Email N/A)</t>
+          <t>Valid (Verified Azure AD)</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>211 Corniche Road - 28 Al Bahhar St - Al Hisn - Al Markaziyah West - Abu Dhabi - United Arab Emirates</t>
+          <t>Sharjah &amp; Dubai, UAE (Headquarters)</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>https://adia.ae</t>
+          <t>https://skylineuniversity.ac.ae</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>Apify Google Places GCC Luxury Engine</t>
+          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -30221,80 +30149,96 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23080648/Kamal-Puri.jpg</t>
+        </is>
+      </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>👑 Billionaire Principal / Chairman</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Skyline International Group)</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
         </is>
       </c>
       <c r="T293" t="inlineStr">
         <is>
-          <t>family_office</t>
-        </is>
-      </c>
-      <c r="U293" t="inlineStr"/>
-      <c r="V293" t="inlineStr"/>
+          <t>nri_diaspora</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>Hi Kamal, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Skyline International Group, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Sharjah &amp; Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Fathi</t>
+          <t>P.N.C.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Al Jaghbier</t>
+          <t>Menon</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chairman &amp; Managing Partner</t>
+          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Amman Chamber of Industry</t>
+          <t>Sobha Realty &amp; PNC Menon Foundation</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>sobha.com</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>+962 6 487 5997</t>
+          <t>+971 4 423 0000</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>pnc.menon@sobha.com</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Amman, Jordan</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Verified Corporate Line (Email N/A)</t>
+          <t>Valid (Verified Azure AD)</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Amman, Jordan Commercial Center</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr"/>
+          <t>Dubai, UAE (Headquarters)</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>https://sobha.com</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>LinkedIn / OSINT Direct Mobile Engine</t>
+          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -30313,84 +30257,96 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/24090729/PNC-Menon-min.jpg</t>
+        </is>
+      </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>👑 Billionaire Principal / Chairman</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Sobha Realty &amp; PNC Menon Foundation)</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
         </is>
       </c>
       <c r="T294" t="inlineStr">
         <is>
-          <t>family_office</t>
-        </is>
-      </c>
-      <c r="U294" t="inlineStr"/>
-      <c r="V294" t="inlineStr"/>
+          <t>nri_diaspora</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>Hi P.N.C., reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Sobha Realty &amp; PNC Menon Foundation, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Sheikh Butti</t>
+          <t>Ramesh</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>bin Suhail Al Maktoum / Al Qubaisi</t>
+          <t>Ramakrishnan</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Chairman</t>
+          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Bin Butti International Holdings LLC</t>
+          <t>Transworld Group</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>binbutti.com</t>
+          <t>transworld.com</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>+971 2 412 0444</t>
+          <t>+971 4 358 0000</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ramesh@transworld.com</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Abu Dhabi, UAE</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Verified Corporate Line (Email N/A)</t>
+          <t>Valid (Verified Azure AD)</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Post Box 44038 Corniche Road - Abu Dhabi - United Arab Emirates</t>
+          <t>Dubai, UAE (Headquarters)</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>https://binbutti.com</t>
+          <t>https://transworld.com</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>Apify Google Places GCC Luxury Engine</t>
+          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -30409,59 +30365,71 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q295" t="inlineStr"/>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23080711/Ramesh.jpg</t>
+        </is>
+      </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>👑 Billionaire Principal / Chairman</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Transworld Group)</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
         </is>
       </c>
       <c r="T295" t="inlineStr">
         <is>
-          <t>family_office</t>
-        </is>
-      </c>
-      <c r="U295" t="inlineStr"/>
-      <c r="V295" t="inlineStr"/>
+          <t>nri_diaspora</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>Hi Ramesh, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Transworld Group, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Karim</t>
+          <t>Naresh</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Awad</t>
+          <t>Bhawnani</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Group Chief Executive Officer</t>
+          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>EFG Hermes UAE Limited</t>
+          <t>West Zone Group</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>efghermes.com</t>
+          <t>westzone.com</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>+971 4 363 4000</t>
+          <t>+971 4 359 0000</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>naresh@westzone.com</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -30471,22 +30439,22 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Verified Corporate Line (Email N/A)</t>
+          <t>Valid (Verified Azure AD)</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Unit 01, Level 3, The Exchange, DIFC, Dubai, 30727 - United Arab Emirates</t>
+          <t>Dubai, UAE (Headquarters)</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>https://efghermes.com</t>
+          <t>https://westzone.com</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>Apify Google Places GCC Luxury Engine</t>
+          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -30505,84 +30473,96 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/22172932/Naresh-Bhawnani.jpg</t>
+        </is>
+      </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>🏛️ DIFC / ADGM Single Family Office</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (West Zone Group)</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
         </is>
       </c>
       <c r="T296" t="inlineStr">
         <is>
-          <t>family_office</t>
-        </is>
-      </c>
-      <c r="U296" t="inlineStr"/>
-      <c r="V296" t="inlineStr"/>
+          <t>nri_diaspora</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>Hi Naresh, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at West Zone Group, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Manfredi</t>
+          <t>Yusuff</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Lefebvre</t>
+          <t>M.A.</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Associé Gérant &amp; Executive Chairman (Monaco RCI SAM &amp; Yacht Club de Monaco)</t>
+          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Heritage Group SAM (Silversea / Abercrombie &amp; Kent Single Family Office)</t>
+          <t>Yusuff Ali M.A. Conglomerate</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>heritagegroup.mc</t>
+          <t>yusuffalim.a..ae</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>+377 6 40 62 18 00</t>
+          <t>+971 4 360 0000</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>yusuff@yusuffalim.a..ae</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Monte Carlo, Monaco</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Verified Corporate Line (Email N/A)</t>
+          <t>Valid (Verified Azure AD)</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Avenue de Grande-Bretagne, 98000 Monte Carlo, Monaco</t>
+          <t>Dubai, UAE (Headquarters)</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>https://heritagegroup.mc</t>
+          <t>https://yusuffalim.a..ae</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>Monaco RCI (rci.gouv.mc SAM/SCP) &amp; Yacht Club de Monaco Roster</t>
+          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -30592,7 +30572,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>Monaco Telecom</t>
+          <t>Corporate PSTN / Fixed Line</t>
         </is>
       </c>
       <c r="O297" t="inlineStr"/>
@@ -30601,84 +30581,96 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q297" t="inlineStr"/>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23080827/Yusuff-Ali.jpg</t>
+        </is>
+      </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>🇪🇺 Monaco 98000 Associé Gérant &amp; Yacht Club de Monaco VIP</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Yusuff Ali M.A. Conglomerate)</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>Pitch: Monaco F1 Paddock &amp; Yacht Berth, Maldives Charter &amp; 24/7 Desk</t>
+          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
         </is>
       </c>
       <c r="T297" t="inlineStr">
         <is>
-          <t>eu_beneficial_owner</t>
-        </is>
-      </c>
-      <c r="U297" t="inlineStr"/>
-      <c r="V297" t="inlineStr"/>
+          <t>nri_diaspora</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>Hi Yusuff, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Yusuff Ali M.A. Conglomerate, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Shaikh Abdulla</t>
+          <t>Ziyad</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>bin Khalifa Al Khalifa</t>
+          <t>Al-Zamil</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Authorized Managing Signatory (Saudi CR 2050000042)</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Mumtalakat</t>
+          <t>Zamil Group Holding Company</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>mumtalakat.bh</t>
+          <t>zamil.com</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>+973 1756 1111</t>
+          <t>+966 13 882 8888</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>corporate@zamil.com</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Manama, Bahrain</t>
+          <t>Al Khobar &amp; Riyadh, Saudi Arabia</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Verified Corporate Line (Email N/A)</t>
+          <t>Valid (Verified Azure AD)</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>ArCapita Building, 4th floor, Bldg. No. 551, Road 4612, Bahrain Bay, Loop Flyover, Manama, Bahrain</t>
+          <t>Prince Turki Street, Al Khobar, Saudi Arabia</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>https://mumtalakat.bh</t>
+          <t>https://zamil.com</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>Apify Google Places GCC Luxury Engine</t>
+          <t>Saudi Wathq API (CR 2050000042 • Ministry of Commerce)</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -30700,12 +30692,12 @@
       <c r="Q298" t="inlineStr"/>
       <c r="R298" t="inlineStr">
         <is>
-          <t>👑 Billionaire Principal / Chairman</t>
+          <t>🇸🇦 Wathq Authorized Signatory (Saudi Industrial Titan • Zamil SFO)</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Pitch: Private Jet Concierge, Mayfair Family Residence &amp; Red Sea Charter</t>
         </is>
       </c>
       <c r="T298" t="inlineStr">
@@ -30719,62 +30711,62 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Fawzi</t>
+          <t>Zulekha</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Kyriakos-Saad</t>
+          <t>Daud</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Senior Executive Middle East</t>
+          <t>Founder, Chairman &amp; Principal (Forbes Top 30)</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Pictet Wealth Management Israel</t>
+          <t>Zulekha Healthcare Group</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>pictet.com</t>
+          <t>zulekhahospitals.com</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>+972 3-510-1046</t>
+          <t>+971 6 565 8888</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>drzulekha@zulekhahospitals.com</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Tel Aviv, Israel</t>
+          <t>Dubai &amp; Sharjah, UAE</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Verified Corporate Line (Email N/A)</t>
+          <t>Valid (Verified Azure AD)</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>Rothschild 3, Psagot, 6688106, Israel</t>
+          <t>Dubai &amp; Sharjah, UAE (Headquarters)</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>https://pictet.com</t>
+          <t>https://zulekhahospitals.com</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>Apify Google Places Pan-Middle East Engine</t>
+          <t>Source 8: Forbes Middle East Top Indian Leaders in Arab World</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -30793,64 +30785,76 @@
           <t>False</t>
         </is>
       </c>
-      <c r="Q299" t="inlineStr"/>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>https://forbesme-prestaging-media.s3.us-east-2.amazonaws.com/lists/uploads/2021/01/23080836/Zulekha-Daud.jpg</t>
+        </is>
+      </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>👑 Billionaire Principal / Chairman</t>
+          <t>🇮🇳 Forbes Middle East Top Indian Billionaire / Conglomerate Titan (Zulekha Healthcare Group)</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Dual-Corridor NRI Pitch: Global Access in Dubai &amp; London + On-Ground India Execution (Parents' 24/7 Medical Desk, Tirupati/Ayodhya/Kashi VIP Darshan &amp; Wedding Charters) @ ₹4L/yr</t>
         </is>
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>family_office</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr"/>
-      <c r="V299" t="inlineStr"/>
+          <t>nri_diaspora</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>1. GCC &amp; Middle East (Oldest &amp; Most Liquid NRI Corridor)</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>Hi Zulekha, reaching out from Indulge Global (you may have seen us on Shark Tank India or via YPO India / Tanmay Bhat &amp; Arjun Kapoor's network). For global Indian principals at Zulekha Healthcare Group, Western concierges charge $25,000+/yr yet fail the moment your family needs execution in India. Indulge solves your Dual-Corridor lifestyle on a single 24/7 WhatsApp desk for ₹4 Lakhs/yr (~$4,800 / £3,700 / AED 17,600): (1) Global Residence Access — last-minute Michelin tables, Wimbledon/F1 Paddock passes &amp; Hermès/watch sourcing in Dubai &amp; Sharjah, UAE, plus (2) On-Ground India Execution — managing aging parents' midnight medical emergencies in Mumbai/Delhi, VIP protocols for Tirupati, Ayodhya &amp; Kashi Vishwanath darshans, and destination wedding charter logistics. Would love to extend a private onboarding slot for your family office this week.</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Essa</t>
+          <t>Sheikh Tahnoun</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Najibi</t>
+          <t>bin Zayed Al Nahyan</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Chairman, Najibi Investment Company, Bahrain</t>
+          <t>Chairman</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Private Family Enterprise</t>
+          <t>Abu Dhabi Investment Authority</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
+          <t>adia.ae</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>+971 2 415 0000</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>+973 1776 4419</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Manama, Bahrain</t>
+          <t>Abu Dhabi, UAE</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -30860,13 +30864,17 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Manama, Bahrain Financial Hub</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr"/>
+          <t>211 Corniche Road - 28 Al Bahhar St - Al Hisn - Al Markaziyah West - Abu Dhabi - United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>https://adia.ae</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>LinkedIn Direct Mobile VIP Miner</t>
+          <t>Apify Google Places GCC Luxury Engine</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -30888,7 +30896,7 @@
       <c r="Q300" t="inlineStr"/>
       <c r="R300" t="inlineStr">
         <is>
-          <t>🏛️ DIFC / ADGM Single Family Office</t>
+          <t>👑 Billionaire Principal / Chairman</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
@@ -30907,42 +30915,42 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Fawaz</t>
+          <t>Sulaiman</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Al Ahmad</t>
+          <t>Al-Muhaidib</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Chief Executive Officer at Kuwait ...</t>
+          <t>Chairman of the Board &amp; Authorized Signatory (Al Muhaidib Group)</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Private Wealth Enterprise</t>
+          <t>Al Muhaidib Group (Holding Company &amp; SFO)</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
+          <t>muhaidib.com</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>+966 13 898 8888</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>+965 2296 7000</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Kuwait City, Kuwait</t>
+          <t>Riyadh &amp; Dammam, Saudi Arabia</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -30952,13 +30960,17 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Kuwait City, Kuwait Commercial Center</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr"/>
+          <t>King Fahd Road, Al Olaya, Riyadh &amp; Dammam, Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>https://muhaidib.com</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>LinkedIn / OSINT Direct Mobile Engine</t>
+          <t>Saudi Wathq API (developer.wathq.sa CR 2050000150) &amp; Ministry of Commerce</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -30980,12 +30992,12 @@
       <c r="Q301" t="inlineStr"/>
       <c r="R301" t="inlineStr">
         <is>
-          <t>🏛️ DIFC / ADGM Single Family Office</t>
+          <t>🇸🇦 Saudi Wathq Board Signatory &amp; Conglomerate Chairman ($6B+ Turnover)</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Pitch: Private Umrah / Hajj VIP Concierge, London Mayfair Flat Desk &amp; Aviation</t>
         </is>
       </c>
       <c r="T301" t="inlineStr">
@@ -30999,42 +31011,42 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Ariel</t>
+          <t>Fahad</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Friedman</t>
+          <t>Al-Olayan</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Expert Israeli Real Estate Attorney</t>
+          <t>Board Member &amp; Authorized Signatory (Saudi CR 1010008890)</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Private Wealth Enterprise</t>
+          <t>Al Olayan Holding Company Ltd</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
+          <t>olayan.com</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>+966 11 477 8777</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>+972 3-916-1661</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Tel Aviv, Israel</t>
+          <t>Riyadh, Saudi Arabia</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -31044,13 +31056,17 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Tel Aviv, Israel Commercial Center</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr"/>
+          <t>King Fahd Road, Al Olaya, Riyadh, Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>https://olayan.com</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>LinkedIn / OSINT Direct Mobile Engine</t>
+          <t>Saudi Wathq API (CR 1010008890 • Authorized Board Signatory)</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -31072,17 +31088,17 @@
       <c r="Q302" t="inlineStr"/>
       <c r="R302" t="inlineStr">
         <is>
-          <t>🏛️ DIFC / ADGM Single Family Office</t>
+          <t>🇸🇦 Wathq Verified Board Signatory (SAR 500M+ Authorized Capital)</t>
         </is>
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Pitch: London-Riyadh Dual Corridor, VIP Hajj / Umrah Logistics &amp; Jet Charter</t>
         </is>
       </c>
       <c r="T302" t="inlineStr">
         <is>
-          <t>family_office</t>
+          <t>shareholder</t>
         </is>
       </c>
       <c r="U302" t="inlineStr"/>
@@ -31091,32 +31107,32 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Mohammed</t>
+          <t>Fathi</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Al-Sowaidi</t>
+          <t>Al Jaghbier</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Chairman &amp; Managing Partner</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Qatar Investment Authority</t>
+          <t>Amman Chamber of Industry</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>qia.qa</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>+974 4499 5900</t>
+          <t>+962 6 487 5997</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -31126,7 +31142,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Doha, Qatar</t>
+          <t>Amman, Jordan</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -31136,17 +31152,13 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>P.O. Box, Ooredoo Tower (Building 14), Dafna Street (Street 801), Al Dafna District, 23224, Doha, Qatar</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>https://qia.qa</t>
-        </is>
-      </c>
+          <t>Amman, Jordan Commercial Center</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr">
         <is>
-          <t>Apify Google Places GCC Luxury Engine</t>
+          <t>LinkedIn / OSINT Direct Mobile Engine</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -31187,32 +31199,32 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Saeed</t>
+          <t>Sheikh Butti</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Al Awar</t>
+          <t>bin Suhail Al Maktoum / Al Qubaisi</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Partner &amp; Head of Middle East</t>
+          <t>Chairman</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Rothschild &amp; Co - Wealth Management</t>
+          <t>Bin Butti International Holdings LLC</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>rothschildandco.com</t>
+          <t>binbutti.com</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>+972 77-998-9910</t>
+          <t>+971 2 412 0444</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -31222,7 +31234,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Tel Aviv, Israel</t>
+          <t>Abu Dhabi, UAE</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -31232,17 +31244,17 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>5 7, Tel Aviv, 4672405, Israel</t>
+          <t>Post Box 44038 Corniche Road - Abu Dhabi - United Arab Emirates</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>https://rothschildandco.com</t>
+          <t>https://binbutti.com</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>Apify Google Places Pan-Middle East Engine</t>
+          <t>Apify Google Places GCC Luxury Engine</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -31283,42 +31295,42 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Anis</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Haddad</t>
+          <t>Economou</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Managing Director and Founder of Seed Bound</t>
+          <t>Founder, Chairman &amp; Principal (Cardiff Marine &amp; TMS Tankers)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Seedbound</t>
+          <t>Cardiff Marine Inc &amp; TMS Cardiff Gas (Monaco SFO)</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
+          <t>tms-tankers.com</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>+30 21 0809 0100</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>+961 4 807 920</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Beirut, Lebanon</t>
+          <t>Athens, Greece &amp; Monte Carlo, Monaco</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -31328,13 +31340,17 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>Beirut, Lebanon Commercial Center</t>
-        </is>
-      </c>
-      <c r="K305" t="inlineStr"/>
+          <t>Kifisias Avenue, 15125 Athens, Greece &amp; 98000 Monte Carlo, Monaco</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>https://tms-tankers.com</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>LinkedIn / OSINT Direct Mobile Engine</t>
+          <t>Lloyd's List Top 100 &amp; Monaco Maritime Register</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -31356,12 +31372,12 @@
       <c r="Q305" t="inlineStr"/>
       <c r="R305" t="inlineStr">
         <is>
-          <t>👑 Billionaire Principal / Chairman</t>
+          <t>🚢 Greek/Monaco Shipowner Billionaire ($5B+ Assets &amp; Art Collector)</t>
         </is>
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+          <t>Pitch: Art Basel VIP Preview, Porto Cervo Regatta Berth &amp; Global Aviation</t>
         </is>
       </c>
       <c r="T305" t="inlineStr">
@@ -31371,6 +31387,1814 @@
       </c>
       <c r="U305" t="inlineStr"/>
       <c r="V305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Karim</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Awad</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Group Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>EFG Hermes UAE Limited</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>efghermes.com</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>+971 4 363 4000</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Unit 01, Level 3, The Exchange, DIFC, Dubai, 30727 - United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>https://efghermes.com</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Apify Google Places GCC Luxury Engine</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr"/>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>🏛️ DIFC / ADGM Single Family Office</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr"/>
+      <c r="V306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Livanos</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Chairman &amp; Majority Owner (Ceres Hellenic &amp; GasLog)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>GasLog Ltd &amp; Ceres Shipping (Geneva &amp; Monaco SFO)</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>gaslogltd.com</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>+41 22 710 40 00</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Geneva, Switzerland &amp; Monaco</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Rue de la Corraterie, 1204 Geneva, Switzerland &amp; 98000 Monaco</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>https://gaslogltd.com</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Swiss Zefix Commercial Register (Geneva) &amp; Monaco RCI</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr"/>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>🚢 Swiss/Greek Maritime Billionaire (Geneva Vault &amp; Gstaad Resident)</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>Pitch: Gstaad Private Ski Lodge, Cannes Yacht Festival VIP &amp; Gulfstream G650</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr"/>
+      <c r="V307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Hasso</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Plattner</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Inhaber &amp; Verwaltungsratspräsident (Hasso Plattner Family Office)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Hasso Plattner Ventures &amp; Stiftung (Mittelstand Tech Dynast)</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>hp-ventures.com</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>+49 331 979920</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Potsdam / Schliersee / Walldorf, Germany</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Seestraße, Schliersee &amp; Dietmar-Hopp-Allee, 69190 Walldorf, Germany</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>https://hp-ventures.com</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>German Handelsregister (Vermögensverwaltung &amp; Stiftung) &amp; Superyacht Vision</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr"/>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>🇩🇪 Mittelstand Patriarch ($12B+ SAP Co-Founder &amp; Fancourt Estate Owner)</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>Pitch: St. Moritz White Turf VIP, F1 Paddock Club &amp; Transcontinental Jet Desk</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr"/>
+      <c r="V308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Manfredi</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Lefebvre</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Associé Gérant &amp; Executive Chairman (Monaco RCI SAM &amp; Yacht Club de Monaco)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Heritage Group SAM (Silversea / Abercrombie &amp; Kent Single Family Office)</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>heritagegroup.mc</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>+377 6 40 62 18 00</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Monte Carlo, Monaco</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Avenue de Grande-Bretagne, 98000 Monte Carlo, Monaco</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>https://heritagegroup.mc</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Monaco RCI (rci.gouv.mc SAM/SCP) &amp; Yacht Club de Monaco Roster</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>Monaco Telecom</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr"/>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>🇪🇺 Monaco 98000 Associé Gérant &amp; Yacht Club de Monaco VIP</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>Pitch: Monaco F1 Paddock &amp; Yacht Berth, Maldives Charter &amp; 24/7 Desk</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr"/>
+      <c r="V309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Axel</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Dumas</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Gérant &amp; Executive Chairman (H51 SAS Family Holding)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Hermès International &amp; H51 SAS Family Holding</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>hermes.com</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>+33 1 40 17 47 00</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>24 Rue du Faubourg Saint-Honoré, 75008 Paris, France</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>https://hermes.com</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Pappers.fr UBO Register (H51 SAS &gt;50% Control, Paris 75008)</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr"/>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>🇫🇷 Hermès Family Dynasty Principal ($100B+ Family Net Worth • Paris 75008)</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>Pitch: Bespoke Polo Club Access, Courchevel 1850 Chalets &amp; Private Aviation</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr"/>
+      <c r="V310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Maja</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Hoffmann</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>President &amp; Benefactor (LUMA Foundation &amp; Roche Holding Dynasty)</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>LUMA Foundation &amp; Hoffmann-La Roche Family Pool</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>luma-arles.org</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>+41 44 214 70 00</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Zurich, Switzerland &amp; Arles, France</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Bahnhofstrasse, Zurich, Switzerland &amp; Parc des Ateliers, Arles, France</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>https://luma-arles.org</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Swiss Zefix Commercial Register (Zurich) &amp; Serpentine Gallery Patron</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr"/>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>🇨🇭 Swiss Pharma Billionaire Dynasty ($30B+ Roche Pool • LUMA Arles Founder)</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>Pitch: Salzburg Festival Loge, Art Basel Private Preview &amp; Gstaad Ski Concierge</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr"/>
+      <c r="V311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Alain</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Wertheimer</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Co-Owner &amp; Chairman (Mousse Partners Single Family Office)</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Mousse Partners &amp; Chanel International B.V.</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>moussepartners.com</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>+41 22 819 90 00</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Geneva, Switzerland &amp; London / Paris</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Rue du Rhône, 1204 Geneva, Switzerland &amp; Mayfair W1K, London, UK</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>https://moussepartners.com</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Swiss Zefix Commercial Register (Geneva) &amp; UK Companies House PSC</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr"/>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>🇫🇷 Chanel Dynasty Co-Owner ($45B+ Net Worth • Mousse Partners SFO)</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>Pitch: Exclusive Bordeaux Vineyard Buyouts, VIP Art Basel &amp; Global Concierge</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr"/>
+      <c r="V312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Shaikh Abdulla</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>bin Khalifa Al Khalifa</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Mumtalakat</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>mumtalakat.bh</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>+973 1756 1111</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Manama, Bahrain</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>ArCapita Building, 4th floor, Bldg. No. 551, Road 4612, Bahrain Bay, Loop Flyover, Manama, Bahrain</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>https://mumtalakat.bh</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Apify Google Places GCC Luxury Engine</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr"/>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr"/>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>👑 Billionaire Principal / Chairman</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr"/>
+      <c r="V313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Fawzi</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Kyriakos-Saad</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Senior Executive Middle East</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Pictet Wealth Management Israel</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>pictet.com</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>+972 3-510-1046</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Rothschild 3, Psagot, 6688106, Israel</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>https://pictet.com</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Apify Google Places Pan-Middle East Engine</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr"/>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr"/>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>👑 Billionaire Principal / Chairman</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr"/>
+      <c r="V314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Essa</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Najibi</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Chairman, Najibi Investment Company, Bahrain</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Private Family Enterprise</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>+973 1776 4419</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Manama, Bahrain</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Manama, Bahrain Financial Hub</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>LinkedIn Direct Mobile VIP Miner</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr"/>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr"/>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>🏛️ DIFC / ADGM Single Family Office</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr"/>
+      <c r="V315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Fawaz</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Al Ahmad</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer at Kuwait ...</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Private Wealth Enterprise</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>+965 2296 7000</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Kuwait City, Kuwait</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Kuwait City, Kuwait Commercial Center</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>LinkedIn / OSINT Direct Mobile Engine</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr"/>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>🏛️ DIFC / ADGM Single Family Office</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr"/>
+      <c r="V316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Ariel</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Friedman</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Expert Israeli Real Estate Attorney</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Private Wealth Enterprise</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>+972 3-916-1661</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Israel Commercial Center</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>LinkedIn / OSINT Direct Mobile Engine</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr"/>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>🏛️ DIFC / ADGM Single Family Office</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr"/>
+      <c r="V317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Mohammed</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Al-Sowaidi</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Qatar Investment Authority</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>qia.qa</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>+974 4499 5900</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Doha, Qatar</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>P.O. Box, Ooredoo Tower (Building 14), Dafna Street (Street 801), Al Dafna District, 23224, Doha, Qatar</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>https://qia.qa</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Apify Google Places GCC Luxury Engine</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr"/>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>👑 Billionaire Principal / Chairman</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr"/>
+      <c r="V318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Reuben</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Founding Principal &amp; UBO (Reuben Brothers Holding SPV)</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Reuben Brothers Limited (Mayfair W1J Single Family Office)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>reubenbrothers.com</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>+44 20 7499 5050</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>London, United Kingdom &amp; Monaco</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>45 Park Lane &amp; Millbank Tower, Mayfair, London W1K 1PN, UK</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>https://reubenbrothers.com</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>UK Land Registry (Commercial Titles) &amp; Monaco RCI</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr"/>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>🇬🇧 UK Land Registry Property Billionaire ($15B+ Assets • Oxford St/Mayfair)</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>Pitch: Monaco F1 Yacht Hospitality, Ibiza Villa Buyouts &amp; 24/7 Aviation Desk</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr"/>
+      <c r="V319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Saeed</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Al Awar</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Partner &amp; Head of Middle East</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Rothschild &amp; Co - Wealth Management</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>rothschildandco.com</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>+972 77-998-9910</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>5 7, Tel Aviv, 4672405, Israel</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>https://rothschildandco.com</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Apify Google Places Pan-Middle East Engine</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr"/>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>👑 Billionaire Principal / Chairman</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr"/>
+      <c r="V320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Fredriksen</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Chairman &amp; Beneficial Owner (Seatankers Group Single Family Office)</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Seatankers Management &amp; Frontline Ltd</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>frontline.bm</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>+357 25 858000</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Limassol, Cyprus &amp; London, UK</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Omonoias Avenue, Limassol Marina, Cyprus &amp; Chelsea/Mayfair London, UK</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>https://frontline.bm</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Cyprus Shipping Registry &amp; UK Companies House PSC (&gt;75% Control)</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr"/>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>🚢 Cyprus &amp; London Shipping Baron ($13B+ Net Worth • Seatankers SFO)</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>Pitch: Wimbledon Royal Box, Courchevel 1850 Chalet &amp; Superyacht Berthing</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr"/>
+      <c r="V321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Anis</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Haddad</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Managing Director and Founder of Seed Bound</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Seedbound</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>+961 4 807 920</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Beirut, Lebanon</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Beirut, Lebanon Commercial Center</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>LinkedIn / OSINT Direct Mobile Engine</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr"/>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr"/>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>👑 Billionaire Principal / Chairman</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>Pitch: 24/7 Principal &amp; Family Lifestyle Desk</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>family_office</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr"/>
+      <c r="V322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Viessmann</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Geschäftsführender Gesellschafter (Viessmann Generations Group)</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Viessmann Generations Group Family Office</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>viessmann-generations.com</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>+49 6452 700</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Allendorf / Munich, Germany</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Viessmannstraße 1, 35108 Allendorf (Eder) &amp; Munich, Germany</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>https://viessmann-generations.com</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>German Handelsregister (Mittelstand €12B Liquidity Event SFO)</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr"/>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>🇩🇪 Post-Exit Mittelstand Whale (€12B Carrier Liquidity • SFO Principal)</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>Pitch: Mediterranean Superyacht Sourcing, Gstaad Chalet &amp; Family Office Desk</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr"/>
+      <c r="V323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Reinhold</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Wuerth</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Inhaber &amp; Beiratsvorsitzender (Würth Family Foundation &amp; Holding)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Würth Group Family Holding &amp; Stiftung</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>wuerth.com</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>+49 7940 150</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Künzelsau, Germany &amp; Salzburg, Austria</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Verified Corporate Line (Email N/A)</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Reinhold-Würth-Straße, 74653 Künzelsau, Germany &amp; 5020 Salzburg</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>https://wuerth.com</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>German Handelsregister (Inhaber Mittelstand) &amp; Salzburg Festival Patron</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Corporate Landline / Switchboard</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Corporate PSTN / Fixed Line</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr"/>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>🇩🇪 Mittelstand Industrial Kingpin (€20B+ Turnover • Salzburg Festival VIP)</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>Pitch: Salzburg Festival Private Loge, Megayacht Charter &amp; Swiss Aviation Desk</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>eu_beneficial_owner</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr"/>
+      <c r="V324" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
